--- a/logical_function.xlsx
+++ b/logical_function.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ARC Institute\logical_method_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9155040D-E00A-4F4C-BB80-DFC166CA884C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE94C7A-3167-4328-AA79-D7DBDC4C7346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -279,7 +279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -304,7 +304,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -585,7 +584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="10" max="10" width="12.5546875" customWidth="1"/>
@@ -593,10 +592,10 @@
     <col min="12" max="12" width="26.44140625" customWidth="1"/>
     <col min="13" max="13" width="11" customWidth="1"/>
     <col min="14" max="14" width="12.77734375" customWidth="1"/>
-    <col min="15" max="15" width="11.5546875" customWidth="1"/>
+    <col min="15" max="15" width="16.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -613,7 +612,7 @@
         <v>0.85416666666666663</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="H2" t="s">
         <v>37</v>
       </c>
@@ -628,7 +627,7 @@
         <v>2.0833333333333332E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="K3" t="s">
         <v>43</v>
       </c>
@@ -636,7 +635,7 @@
         <v>0.20833333333333334</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -679,8 +678,9 @@
       <c r="N4" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>101</v>
       </c>
@@ -727,20 +727,20 @@
         <f>IF(M5&gt;L$2,"I can travel","I can't travel")</f>
         <v>I can't travel</v>
       </c>
-      <c r="O5" t="str">
+      <c r="O5" s="3" t="str">
+        <f>IF(M5&gt;L$1,"BEST FOR TRAVEL",IF(M5&gt;L$3,"WASTE"," can't travel"))</f>
+        <v xml:space="preserve"> can't travel</v>
+      </c>
+      <c r="S5" t="str">
         <f>IF(M5&gt;L2=MIN(M5:M10,),"I can travel","I can't travel")</f>
         <v>I can't travel</v>
       </c>
-      <c r="P5">
+      <c r="T5">
         <f>_xlfn.RANK.EQ(M5,M$5:M$10,0)</f>
         <v>5</v>
       </c>
-      <c r="Q5" t="str">
-        <f>IF(L$1&lt;M5,"wste of time",IF(L$3&gt;M5,"best for travel"," can't travel"))</f>
-        <v>best for travel</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>102</v>
       </c>
@@ -787,20 +787,20 @@
         <f t="shared" ref="N6:N11" si="3">IF(M6&gt;L$2,"I can travel","I can't travel")</f>
         <v>I can travel</v>
       </c>
-      <c r="O6" t="str">
-        <f t="shared" ref="O6:O10" si="4">IF(M6&gt;L3=MIN(M6:M11,),"I can travel","I can't travel")</f>
+      <c r="O6" s="3" t="str">
+        <f>IF(M6&lt;L$1,"BEST FOR TRAVEL",IF(M6&gt;L$3,"WASTE"," can't travel"))</f>
+        <v>BEST FOR TRAVEL</v>
+      </c>
+      <c r="S6" t="str">
+        <f>IF(M6&gt;L3=MIN(M6:M11,),"I can travel","I can't travel")</f>
         <v>I can't travel</v>
       </c>
-      <c r="P6">
-        <f t="shared" ref="P6:P11" si="5">_xlfn.RANK.EQ(M6,M$5:M$10,0)</f>
+      <c r="T6">
+        <f>_xlfn.RANK.EQ(M6,M$5:M$10,0)</f>
         <v>4</v>
       </c>
-      <c r="Q6" t="str">
-        <f>IF(M6&lt;=L1,"wste of time",IF(M6&lt;L$3,"best for travel"," can't travel"))</f>
-        <v>wste of time</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>103</v>
       </c>
@@ -847,20 +847,20 @@
         <f t="shared" si="3"/>
         <v>I can travel</v>
       </c>
-      <c r="O7" t="str">
-        <f t="shared" si="4"/>
+      <c r="O7" s="3" t="str">
+        <f t="shared" ref="O7:O10" si="4">IF(M7&gt;L$1,"BEST FOR TRAVEL",IF(M7&gt;L$3,"WASTE"," can't travel"))</f>
+        <v>WASTE</v>
+      </c>
+      <c r="S7" t="str">
+        <f>IF(M7&gt;L4=MIN(M7:M12,),"I can travel","I can't travel")</f>
         <v>I can't travel</v>
       </c>
-      <c r="P7">
-        <f t="shared" si="5"/>
+      <c r="T7">
+        <f>_xlfn.RANK.EQ(M7,M$5:M$10,0)</f>
         <v>2</v>
       </c>
-      <c r="Q7" t="str">
-        <f t="shared" ref="Q6:Q10" si="6">IF(L$1&lt;M7,"wste of time",IF(L$3&gt;M7,"best for travel"," can't travel"))</f>
-        <v xml:space="preserve"> can't travel</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>104</v>
       </c>
@@ -907,20 +907,20 @@
         <f t="shared" si="3"/>
         <v>I can travel</v>
       </c>
-      <c r="O8" t="str">
+      <c r="O8" s="3" t="str">
         <f t="shared" si="4"/>
+        <v>WASTE</v>
+      </c>
+      <c r="S8" t="str">
+        <f>IF(M8&gt;L5=MIN(M8:M13,),"I can travel","I can't travel")</f>
         <v>I can't travel</v>
       </c>
-      <c r="P8">
-        <f t="shared" si="5"/>
+      <c r="T8">
+        <f>_xlfn.RANK.EQ(M8,M$5:M$10,0)</f>
         <v>1</v>
       </c>
-      <c r="Q8" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve"> can't travel</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>105</v>
       </c>
@@ -967,20 +967,20 @@
         <f t="shared" si="3"/>
         <v>I can't travel</v>
       </c>
-      <c r="O9" t="str">
+      <c r="O9" s="3" t="str">
         <f t="shared" si="4"/>
+        <v xml:space="preserve"> can't travel</v>
+      </c>
+      <c r="S9" t="str">
+        <f>IF(M9&gt;L6=MIN(M9:M14,),"I can travel","I can't travel")</f>
         <v>I can't travel</v>
       </c>
-      <c r="P9">
-        <f t="shared" si="5"/>
+      <c r="T9">
+        <f>_xlfn.RANK.EQ(M9,M$5:M$10,0)</f>
         <v>6</v>
       </c>
-      <c r="Q9" t="str">
-        <f>IF(L$1&lt;M9,"wste of time",IF(L$3&gt;M9,"best for travel"," can't travel"))</f>
-        <v>best for travel</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>106</v>
       </c>
@@ -1027,33 +1027,23 @@
         <f t="shared" si="3"/>
         <v>I can travel</v>
       </c>
-      <c r="O10" t="str">
+      <c r="O10" s="3" t="str">
         <f t="shared" si="4"/>
+        <v>WASTE</v>
+      </c>
+      <c r="S10" t="str">
+        <f>IF(M10&gt;L7=MIN(M10:M15,),"I can travel","I can't travel")</f>
         <v>I can't travel</v>
       </c>
-      <c r="P10">
-        <f t="shared" si="5"/>
+      <c r="T10">
+        <f>_xlfn.RANK.EQ(M10,M$5:M$10,0)</f>
         <v>3</v>
       </c>
-      <c r="Q10" t="str">
-        <f t="shared" si="6"/>
-        <v xml:space="preserve"> can't travel</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="M11" s="5">
-        <f>MIN(M5:M10)</f>
-        <v>-0.14236111111111116</v>
-      </c>
-      <c r="N11" s="7" t="str">
-        <f t="shared" si="3"/>
-        <v>I can't travel</v>
-      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="M11" s="5"/>
+      <c r="N11" s="7"/>
       <c r="O11" s="5"/>
-      <c r="P11">
-        <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1310,8 +1300,6 @@
       <c r="Q11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
     </row>
     <row r="12" spans="8:19" x14ac:dyDescent="0.3">
       <c r="M12" s="3" t="s">
